--- a/data/trans_bre/P59A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,01</t>
+          <t>-8,47; 1,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 4,52</t>
+          <t>-8,08; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 1,8</t>
+          <t>-10,19; 2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 4,31</t>
+          <t>-6,46; 4,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,92; 18,93</t>
+          <t>-68,28; 18,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 44,87</t>
+          <t>-46,48; 50,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 14,26</t>
+          <t>-47,98; 19,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 45,5</t>
+          <t>-40,56; 46,66</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 1,74</t>
+          <t>-7,37; 2,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 2,21</t>
+          <t>-7,7; 2,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,98</t>
+          <t>-6,16; 4,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,62</t>
+          <t>-6,79; 4,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 22,86</t>
+          <t>-51,64; 25,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 17,63</t>
+          <t>-43,34; 21,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 29,11</t>
+          <t>-33,15; 30,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 34,63</t>
+          <t>-34,2; 36,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 2,65</t>
+          <t>-9,17; 2,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 2,4</t>
+          <t>-10,97; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 1,36</t>
+          <t>-9,14; 2,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 5,15</t>
+          <t>-9,5; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 26,75</t>
+          <t>-52,18; 28,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 18,27</t>
+          <t>-49,01; 14,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 10,39</t>
+          <t>-44,32; 16,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 31,56</t>
+          <t>-38,42; 30,0</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 0,17</t>
+          <t>-8,99; 0,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,93</t>
+          <t>-2,7; 7,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -0,24</t>
+          <t>-9,72; -0,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,67; -0,95</t>
+          <t>-9,92; -0,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 1,23</t>
+          <t>-44,93; 2,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 69,19</t>
+          <t>-15,97; 64,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -0,29</t>
+          <t>-45,52; -1,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,63; -7,42</t>
+          <t>-57,59; -7,12</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,97</t>
+          <t>-6,08; -0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,92</t>
+          <t>-3,79; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,77</t>
+          <t>-6,25; -0,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,06</t>
+          <t>-5,78; 0,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -7,94</t>
+          <t>-40,28; -6,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 14,41</t>
+          <t>-22,49; 13,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,18; -4,5</t>
+          <t>-33,24; -5,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -0,59</t>
+          <t>-32,82; 0,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P59A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>-7,88%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 1,03</t>
+          <t>-8,69; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 5,29</t>
+          <t>-7,47; 5,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 2,21</t>
+          <t>-10,6; 1,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,17</t>
+          <t>-6,6; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 18,96</t>
+          <t>-70,83; 15,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 50,33</t>
+          <t>-45,56; 53,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 19,25</t>
+          <t>-49,53; 12,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,56; 46,66</t>
+          <t>-39,02; 50,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,28%</t>
+          <t>-8,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,06</t>
+          <t>-7,71; 1,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,75</t>
+          <t>-7,98; 2,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 4,15</t>
+          <t>-6,78; 4,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 4,85</t>
+          <t>-6,79; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 25,35</t>
+          <t>-53,01; 21,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 21,93</t>
+          <t>-43,9; 21,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 30,09</t>
+          <t>-34,41; 28,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 36,26</t>
+          <t>-33,65; 30,63</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-12,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 2,49</t>
+          <t>-10,08; 2,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 2,02</t>
+          <t>-10,48; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 2,45</t>
+          <t>-8,98; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 4,59</t>
+          <t>-8,83; 3,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,18; 28,63</t>
+          <t>-53,78; 21,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 14,48</t>
+          <t>-47,95; 18,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 16,33</t>
+          <t>-45,11; 16,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 30,0</t>
+          <t>-36,96; 24,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-5,31</t>
+          <t>-4,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-35,28%</t>
+          <t>-27,64%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 0,38</t>
+          <t>-9,48; 0,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,31</t>
+          <t>-2,26; 7,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,25</t>
+          <t>-9,92; 0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,92; -0,91</t>
+          <t>-8,98; 0,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 2,03</t>
+          <t>-46,47; 1,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 64,31</t>
+          <t>-14,18; 62,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -1,16</t>
+          <t>-46,05; 0,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,59; -7,12</t>
+          <t>-47,76; 2,09</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-15,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,73</t>
+          <t>-6,01; -0,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,88</t>
+          <t>-3,86; 2,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,79</t>
+          <t>-6,09; -0,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,05</t>
+          <t>-5,1; 0,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -6,54</t>
+          <t>-39,84; -6,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 13,25</t>
+          <t>-23,19; 15,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -5,1</t>
+          <t>-32,59; -4,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 0,95</t>
+          <t>-28,53; 2,49</t>
         </is>
       </c>
     </row>
